--- a/10_Work/uc对局复盘/jsontest/result.xlsx
+++ b/10_Work/uc对局复盘/jsontest/result.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程保持高压态势，不给反扑空间 3:0 轻松收官。整体稍显不足，但资源管理能力较为突出。\n【优势点】资源管理能力打出 6.2 分，对手取得 4.1 分，策略更具水准，该维度思路清晰发挥亮眼。\n【劣势点】博弈能力 4.5 分不敌对手 9.2 分，后续打磨会有更大突破。","is_rule":true},{"content":"【亮眼表现】\n我方处于无法脱出的受击状态共 5.5 秒（对手 0.0 秒），通过合理防守与脱出手段，有效缩短受制时间。","jump_points":[1],"label_id":28},{"content":"【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程保持高压态势，不给反扑空间 3:0 轻松收官。整体稍显不足，但资源管理能力表现突出。\n【优势点】资源管理能力打出 6.2 分，对手取得 4.1 分，策略更具水准，该维度思路清晰发挥亮眼。\n【劣势点】博弈能力 4.5 分不敌对手 9.2 分，后续打磨会有更大突破。", "is_rule": true}, {"content": "【亮眼表现】\n我方处于无法脱出的受击状态共 5.5 秒（对手 0.0 秒），通过合理防守与脱出手段，有效缩短受制时间。", "jump_points": [1], "label_id": 28, "label_name": "无法脱出总受击时间"}, {"content": "【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n实力差距较为明显，拼尽全力仍 0:3 不敌对手。\n【优势点】博弈能力 9.2 比 4.5 领先对手，表现明显占优，该维度展现顶尖水准。\n【劣势点】资源管理能力 4.1 分不敌对手 6.2 分，优化运营策略就能进步。","is_rule":true},{"content":"【亮眼表现】\n我方打断对手获取先手次数为 4 次（对方 1 次），打断判断与执行尚可。","jump_points":[1],"label_id":23},{"content":"【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n实力差距较为明显， 0:3 不敌对手。\n【优势点】博弈能力 9.2 比 4.5 领先对手，表现明显占优，展现了顶级的博弈水准。\n【劣势点】资源管理能力 4.1 分不敌对手 6.2 分，优化运营策略就能进步。", "is_rule": true}, {"content": "【亮眼表现】\n我方打断对手获取先手次数为 4 次（对方 1 次），打断判断与执行尚可。", "jump_points": [1], "label_id": 23, "label_name": "打断对手获取先手次数"}, {"content": "【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n三盘发挥毫无破绽，以 3:0 横扫对手拿下胜利。\n【优势点】输出能力斩获 7.9 分，对手仅得 4.6 分，输出冲击力更强，该维度表现十分亮眼。\n【劣势点】博弈能力 4.4 分 vs 对手 8.7 分，差距较为明显，博弈思路需重点提升。","is_rule":true},{"content":"【亮眼表现】\n我方本局连段成功率 100%（对手 42.9%），招式衔余更稳定，失误少。","jump_points":[1],"label_id":7},{"content":"【有待提升】\n当前防反触发次数偏少，若能更好把握平招的防反时机，可在成功防御后打出反击压制对手。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n三盘发挥毫无破绽，以 3:0 横扫对手拿下胜利。\n【优势点】输出能力斩获 7.9 分，对手仅得 4.6 分，输出冲击力更强，该维度表现十分亮眼。\n【劣势点】博弈能力 4.4 分 vs 对手 8.7 分，差距较为明显，博弈思路需重点提升。", "is_rule": true}, {"content": "【亮眼表现】\n我方本局连段成功率 100%（对手 42.9%），招式衔接更为稳定，失误少。", "jump_points": [1], "label_id": 7, "label_name": "连段成功率"}, {"content": "【有待提升】\n当前防反触发次数偏少，若能更好把握平招的防反时机，可在成功防御后打出反击压制对手。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程处于被动局面，奋力抵抗仍 0:3 遗憾告负。\n【优势点】博弈能力 8.7 分 vs 对手 4.4 分，表现处于上风，该维度发挥极为出色。\n【劣势点】输出能力 4.6 分不敌对手 7.9 分，强化输出节奏会更具威胁。","is_rule":true},{"content":"【亮眼表现】\n我方打断对手获取先手次数为 4 次（对方 1 次），对招式时机的出色把控多次夺回局势主动权。","jump_points":[1],"label_id":23},{"content":"【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n实力差距较为明显，0：3告负。\n【优势点】博弈能力 8.7 分 vs 对手 4.4 分，以出色的水平压过对手。\n【劣势点】输出能力 4.6 分不敌对手 7.9 分，强化输出节奏会更具威胁。", "is_rule": true}, {"content": "【亮眼表现】\n我方打断对手获取先手次数为 4 次（对方 1 次），对招式时机有着出色的把控，能多次夺回局势主动权。", "jump_points": [1], "label_id": 23, "label_name": "打断对手获取先手次数"}, {"content": "【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n三盘发挥毫无破绽，以 3:0 横扫对手拿下胜利。\n【优势点】博弈能力 7.9 分 vs 对手 3 分，表现处于领先位置，该维度展现超强水准。\n【劣势点】防守能力以 3 比 3 对阵对手，双方发挥接近，势均力敌。","is_rule":true},{"content":"【亮眼表现】\n我方打断对手获取先手次数为 2 次（对方 0 次），对拼判断更敏锐，强行扭转攻防态势。","jump_points":[1],"label_id":23},{"content":"【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n三盘发挥毫无破绽，以 3:0 横扫对手拿下胜利。\n【优势点】博弈能力 7.9 分 vs 对手 3 分，表现处于领先位置，该维度展现超强水准。\n【劣势点】防守能力以 3 比 3 对阵对手，双方发挥接近，势均力敌。", "is_rule": true}, {"content": "【亮眼表现】\n我方打断对手获取先手次数为 2 次（对方 0 次），对拼时的判断更敏锐，可以强行扭转攻防态势。", "jump_points": [1], "label_id": 23, "label_name": "打断对手获取先手次数"}, {"content": "【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程处于被动局面，奋力抵抗仍 0:3 遗憾告负。本次对战你的所有维度数据均低于对局均值，整体表现尚有较大进步空间，持续练习即可稳步变强。","is_rule":true},{"content":"【亮眼表现】\n全局表现尚有巨大余力，各项数据都有极高提升空间。","jump_points":[1]},{"content":"【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n实力差距较为明显，0：3告负。本次对战你的所有维度数据均低于对局均值，整体表现尚有较大进步空间，持续练习即可稳步变强。", "is_rule": true}, {"content": "【亮眼表现】\n全局表现尚有上升余力，持续练习则能更进一步。", "jump_points": [1]}, {"content": "【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程掌控节奏，不给对手任何机会，以 3:0 干净利落取胜。\n【优势点】输出能力 7.9 分 vs 对手 3 分，输出表现一马当先，该维度发挥堪称顶尖。\n【劣势点】防守能力以 3 比 3 对阵对手，双方发挥接近，势均力敌。","is_rule":true},{"content":"【亮眼表现】\n我方本局连段成功率 100%（对手 0%），在进攻端始终保持稳定输出。","jump_points":[1],"label_id":7},{"content":"【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程掌控节奏，不给对手任何机会，以 3:0 干净利落取胜。\n【优势点】输出能力 7.9 分 vs 对手 3 分，输出表现一马当先，该维度发挥堪称顶尖。\n【劣势点】防守能力以 3 比 3 对阵对手，双方发挥接近，势均力敌。", "is_rule": true}, {"content": "【亮眼表现】\n我方本局连段成功率 100%（对手 0%），在进攻端始终可以保持稳定输出，进攻能力出色。", "jump_points": [1], "label_id": 7, "label_name": "连段成功率"}, {"content": "【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n面对对手全面压制，全力抵抗仍 0:3 遗憾落败。本次对战你的所有维度数据均低于对局均值，整体表现尚有较大进步空间，持续练习即可稳步变强。","is_rule":true},{"content":"【亮眼表现】\n暂时落后于平均水平，通过细节打磨，调整空间巨大。","jump_points":[1]},{"content":"【有待提升】\n脱出后体力并不占优，可利用脱出后的保护拉开距离寻找机会，避免贸然反击再次被对手先手。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n对手全面压制，0：3告负。本次对战你的所有维度数据均低于对局均值，整体表现尚有较大进步空间，持续练习即可稳步变强。", "is_rule": true}, {"content": "【亮眼表现】\n暂时落后于平均水平，通过细节打磨，提升潜力巨大。", "jump_points": [1]}, {"content": "【有待提升】\n脱出后体力并不占优，可利用脱出后的保护拉开距离寻找机会，避免贸然反击再次被对手先手。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n面对对手全面压制，全力抵抗仍 0:3 遗憾落败。\n【优势点】博弈能力以 7.9 比 7.9 对阵对手，整体表现接近，难分高下。\n【劣势点】输出能力 5.8 分对比对手 7.9 分，优化输出思路会更强势。","is_rule":true},{"content":"【亮眼表现】\n目前数据低于预期，各项数据均有上扬空间，稍加调整即可持续提升。","jump_points":[1]},{"content":"【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n对手全面压制，0：3告负。\n【优势点】博弈能力以 7.9 比 7.9 对阵对手，整体表现接近，难分高下。\n【劣势点】输出能力 5.8 分对比对手 7.9 分，优化输出思路会更强势。", "is_rule": true}, {"content": "【亮眼表现】\n目前数据低于预期，各项数据均有上扬空间，稍加调整即可稳定提升。", "jump_points": [1]}, {"content": "【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程掌控节奏，不给对手任何机会，以 3:0 干净利落取胜。\n【优势点】输出能力斩获 7.9 分，对手仅得 5.8 分，输出端更具威胁，该维度表现十分优异。\n【劣势点】防守能力以 3 比 3 对阵对手，整体表现接近，难分高下。","is_rule":true},{"content":"【亮眼表现】\n平均连段伤害对比：我方 770（对手 35），每一次出手都更具威胁性。","jump_points":[1],"label_id":10},{"content":"【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程掌控节奏，不给对手任何机会，以 3:0 干净利落取胜。\n【优势点】输出能力斩获 7.9 分，对手仅得 5.8 分，输出端更具威胁，该维度表现十分优异。\n【劣势点】防守能力以 3 比 3 对阵对手，整体表现接近，难分高下。", "is_rule": true}, {"content": "【亮眼表现】\n平均连段伤害对比：我方 770（对手 35），显然每一次出手都更具威胁性。", "jump_points": [1], "label_id": 10, "label_name": "平均连段伤害"}, {"content": "【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n掌控全场节奏，抓住赛点机会，3:1 果断终结对决。你本场各项数据全面超越对手，表现出色，在对局中占据绝对优势。\n【优势点】输出能力斩获 6.7 分，对手仅得 4.4 分，攻坚更占上风，该维度输出端表现优异。","is_rule":true},{"content":"【亮眼表现】\n我方本局连段成功率 50%（对手 31.2%），体现了更扎实的基本功与更冷静的临场判断。","jump_points":[1],"label_id":7},{"content":"【有待提升】\n当前防反触发次数偏少，若能更好把握平招的防反时机，可在成功防御后打出反击压制对手。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n掌控全场节奏，抓住赛点机会，3:1 果断终结对决。你本场各项数据全面超越对手，表现出色，在对局中占据绝对优势。\n【优势点】输出能力斩获 6.7 分，对手仅得 4.4 分，攻坚更占上风，该维度输出端表现优异。", "is_rule": true}, {"content": "【亮眼表现】\n我方本局连段成功率 50%（对手 31.2%），体现了更扎实的基本功与更冷静的临场判断。", "jump_points": [1], "label_id": 7, "label_name": "连段成功率"}, {"content": "【有待提升】\n当前防反触发次数偏少，若能更好把握平招的防反时机，可在成功防御后打出反击压制对手。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n连丢两局后扳回一城，未能延续势头 1:3 失利。本次对战数据全面落后，需及时总结不足，在后续对局中精进表现。\n【劣势点】输出能力 4.4 分对比对手 6.7 分，优化输出思路会更强势。","is_rule":true},{"content":"【亮眼表现】\n起身压制成功次数对比：我方 13 次，对手 10 次，应对起身博弈思路较为清晰。","jump_points":[1],"label_id":6},{"content":"【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n连丢两局后扳回一城，未能延续势头 1:3 失利。本次对战数据全面落后，需及时总结不足，在后续对局中精进表现。\n【劣势点】输出能力 4.4 分对比对手 6.7 分，优化输出思路会更强势。", "is_rule": true}, {"content": "【亮眼表现】\n起身压制成功次数对比：我方 13 次，对手 10 次，应对起身博弈思路较为清晰。", "jump_points": [1], "label_id": 6, "label_name": "起身压制成功次数"}, {"content": "【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n双方实力旗鼓相当，凭借决胜表现 3:2 笑到最后。\n【优势点】输出能力斩获 7.7 分，对手仅得 4.2 分，输出端更具威胁，该维度表现十分优异。\n【劣势点】博弈能力 5.9 分对阵对手 8.0 分，稍加练习就能实现提升。","is_rule":true},{"content":"【亮眼表现】\n我方本局连段成功率 72%（对手 31.2%），在进攻端始终保持稳定输出。","jump_points":[1],"label_id":7},{"content":"【有待提升】\n本局打断对手获取先手次数比为 我方12次:对方30次，需多加练习。把对手和自己的招式摸清楚，先手机会自然会更多。","jump_points":[9],"is_rule":true,"label_id":23}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n双方实力旗鼓相当，凭借决胜表现 3:2 笑到最后。\n【优势点】输出能力斩获 7.7 分，对手仅得 4.2 分，输出端更具威胁，该维度表现十分优异。\n【劣势点】博弈能力 5.9 分对阵对手 8.0 分，稍加练习就能实现提升。", "is_rule": true}, {"content": "【亮眼表现】\n我方本局连段成功率 72%（对手 31.2%），在进攻端始终可以保持稳定输出，进攻能力出色。", "jump_points": [1], "label_id": 7, "label_name": "连段成功率"}, {"content": "【有待提升】\n本场打断对手获取先手次数：我方 12次，对手 30次，难以掌握主动权，需提高截击效率。建议熟悉双方招式的出手特点，从而在博弈中把节奏握在手里。", "jump_points": [9], "is_rule": true, "label_id": 23, "label_name": "打断对手获取先手次数"}]}</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n势均力敌战至最后，因微弱差距 2:3 惜败。\n【优势点】博弈能力斩获 8.0 分，对手仅得 5.9 分，发挥更占优势，该维度表现极为亮眼。\n【劣势点】输出能力 4.2 分对比对手 7.7 分，强化输出节奏即可提升。","is_rule":true},{"content":"【亮眼表现】\n我方打断对手获取先手次数为 30 次（对方 12 次），对时机的把控较为不错。","jump_points":[1],"label_id":23},{"content":"【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n势均力敌战至最后，因微弱差距 2:3 惜败。\n【优势点】博弈能力斩获 8.0 分，对手仅得 5.9 分，发挥更占优势，全方位压制了对手。\n【劣势点】输出能力 4.2 分对比对手 7.7 分，强化输出节奏即可提升。", "is_rule": true}, {"content": "【亮眼表现】\n我方打断对手获取先手次数为 30 次（对方 12 次），对时机的把控较为不错。", "jump_points": [1], "label_id": 23, "label_name": "打断对手获取先手次数"}, {"content": "【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n节奏始终占优，以压倒性实力 3:0 速战速决。\n【优势点】博弈能力取得 8.3 分，对手拿下 4.4 分，表现更胜一筹，该维度展现超凡水准。\n【劣势点】防守能力 4.5 分 vs 对手 4.9 分，双方表现略有微小差距。","is_rule":true},{"content":"【亮眼表现】\n我方打断对手获取先手次数为 13 次（对方 4 次），在对拼中精准截击夺回节奏。","jump_points":[1],"label_id":23},{"content":"【有待提升】\n脱出后体力并不占优，可利用脱出后的保护拉开距离寻找机会，避免贸然反击再次被对手先手。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n节奏始终占优，以压倒性实力 3:0 速战速决。\n【优势点】博弈能力取得 8.3 分，对手拿下 4.4 分，表现高出一档，表现出了非凡的水准。\n【劣势点】防守能力 4.5 分 vs 对手 4.9 分，双方表现基本持平。", "is_rule": true}, {"content": "【亮眼表现】\n我方打断对手获取先手次数为 13 次（对方 4 次），多次精准截击，在对拼中成功夺回节奏。", "jump_points": [1], "label_id": 23, "label_name": "打断对手获取先手次数"}, {"content": "【有待提升】\n脱出后体力并不占优，可利用脱出后的保护拉开距离寻找机会，避免贸然反击再次被对手先手。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n暂时失利调整状态，全力以赴迎接下一场对决。整体稍显不足，但防守能力较为突出。\n【优势点】防守能力以 4.9 比 4.5 领先对手，临场发挥稳健，防守应对稍占上风。\n【劣势点】博弈能力 4.4 分对比对手 8.3 分，调整思路后就能快速进步。","is_rule":true},{"content":"【亮眼表现】\n我方强制脱出后安全率为 60%（对手 50%），脱出后的生存把控尚可。","jump_points":[1],"label_id":19},{"content":"【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n暂时失利调整状态，全力以赴迎接下一场对决。整体稍显不足，但防守能力表现突出。\n【优势点】防守能力 4.9 比 4.5 领先对手，临场发挥势均力敌，防守应对都很稳健。\n【劣势点】博弈能力 4.4 分对比对手 8.3 分，坚持练习，对手绝非遥不可及。", "is_rule": true}, {"content": "【亮眼表现】\n我方强制脱出后安全率为 60%（对手 50%），脱出后的生存把控尚可。", "jump_points": [1], "label_id": 19, "label_name": "脱出后安全率"}, {"content": "【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n战至平局后节奏失守，连输两局 1:3 落败。\n【优势点】输出能力 8.4 比 6.9 对阵对手，发挥稳健扎实，输出表现略胜一筹。\n【劣势点】博弈能力 5.3 分对阵对手 8.2 分，稍加练习就能实现提升。","is_rule":true},{"content":"【亮眼表现】\n我方本局连段成功率 86.7%（对手 64.7%），招式衔接相对流畅，失误控制较好。","jump_points":[1],"label_id":7},{"content":"【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n战至平局后节奏失守，连输两局 1:3 落败。\n【优势点】输出能力 8.4 比 6.9 与对手持平，发挥稳健扎实，输出表现势均力敌。\n【劣势点】博弈能力 5.3 分对阵对手 8.2 分，稍加练习就能实现提升。", "is_rule": true}, {"content": "【亮眼表现】\n我方本局连段成功率 86.7%（对手 64.7%），招式衔接相对流畅，失误较少。", "jump_points": [1], "label_id": 7, "label_name": "连段成功率"}, {"content": "【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n中期稳住局面打出优势，一鼓作气 3:1 终结比赛。\n【优势点】博弈能力斩获 8.2 分，对手拿下 5.3 分，表现优于对手，该维度表现堪称优秀。\n【劣势点】输出能力 6.9 分 vs 对手 8.4 分，发挥稳健扎实，略微处于下风。","is_rule":true},{"content":"【亮眼表现】\n我方打断对手获取先手次数为 16 次（对方 9 次），精准截击让对手攻势屡屡失效。","jump_points":[1],"label_id":23},{"content":"【有待提升】\n本局连段成功率：64.7%（我方），86.7%（对手），减少失误。了解招式对倒地敌人的判定，再配合取消操作，连段会顺很多。","jump_points":[7,9],"is_rule":true,"label_id":7}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n中期稳住局面打出优势，一鼓作气 3:1 终结比赛。\n【优势点】博弈能力斩获 8.2 分，对手拿下 5.3 分，表现优于对手，且自身非常优秀。\n【劣势点】输出能力 6.9 分 vs 对手 8.4 分，发挥稳健扎实，略微处于下风。", "is_rule": true}, {"content": "【亮眼表现】\n我方打断对手获取先手次数为 16 次（对方 9 次），精准截击让对手攻势屡屡失效。", "jump_points": [1], "label_id": 23, "label_name": "打断对手获取先手次数"}, {"content": "【有待提升】\n在对手体力见底或连段压制时使用绝技，可以提升绝技命中率并扩大对局优势。", "jump_points": [2, 10], "is_rule": true, "label_id": 29, "label_name": "炁满时累积伤害量"}]}</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n面对对手全面压制，全力抵抗仍 0:3 遗憾落败。本场对局数据全方位落后对手，发挥存在不足，后续需打磨操作细节。\n【劣势点】博弈能力 3.4 分不敌对手 7.6 分，后续打磨会有更大突破。","is_rule":true},{"content":"【亮眼表现】\n最大连段伤害为我方 340（对手 338），展现了你具备打出爆发伤害的能力。","jump_points":[1],"label_id":11},{"content":"【有待提升】\n防反触发次数较低，熟悉平招的防反时机，可在防御成功后及时打出防御反击进行反制。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n对手全面压制，0：3告负。本场对局数据全方位落后对手，发挥存在不足，后续需打磨操作细节。\n【劣势点】博弈能力 3.4 分不敌对手 7.6 分，后续打磨会有更大突破。", "is_rule": true}, {"content": "【亮眼表现】\n最大连段伤害为我方 340（对手 338），展现了不俗的爆发伤害能力。", "jump_points": [1], "label_id": 11, "label_name": "最大连段伤害"}, {"content": "【有待提升】\n防反触发次数较低，熟悉平招的防反时机，可在防御成功后及时打出防御反击进行反制。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程掌控节奏，不给对手任何机会，以 3:0 干净利落取胜。你在对局中各项数据均优于敌方，凭借出色发挥牢牢占据主动。\n【优势点】博弈能力 7.6 比 3.4 领先对手，表现明显占优，该维度展现顶尖水准。","is_rule":true},{"content":"【亮眼表现】\n我方打断对手获取先手次数为 8 次（对方 3 次），在对拼中精准截击夺回节奏。","jump_points":[1],"label_id":23},{"content":"【有待提升】\n本场最大连段伤害：我方 338，对手 340，可围绕核心高伤技能构建连招，不妨在普攻连段里穿插技能，或把绝技带进连段，伤害会明显更高。","jump_points":[8,9],"is_rule":true,"label_id":11}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程掌控节奏，不给对手任何机会，以 3:0 干净利落取胜。你在对局中各项数据均优于敌方，凭借出色发挥牢牢占据主动权。\n【优势点】博弈能力 7.6 比 3.4 领先对手，表现明显占优，展现了顶级的博弈水准。", "is_rule": true}, {"content": "【亮眼表现】\n我方打断对手获取先手次数为 8 次（对方 3 次），多次精准截击，在对拼中成功夺回节奏。", "jump_points": [1], "label_id": 23, "label_name": "打断对手获取先手次数"}, {"content": "【有待提升】\n本局最大连段伤害对比：我方 338 vs 对方 340，极限连招的输出转化效率还有提升空间。把技能和绝技融进普攻连段里，更容易打出高伤害的完整连段。", "jump_points": [8, 9], "is_rule": true, "label_id": 11, "label_name": "最大连段伤害"}]}</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n被追平后迅速调整状态，连胜两局 3:1 锁定胜局。\n【优势点】博弈能力斩获 8.3 分，对手拿下 5.1 分，表现优于对手，该维度表现堪称优秀。\n【劣势点】资源管理能力 6.3 分对对手 6.8 分，表现可圈可点，稍稍落后些许。","is_rule":true},{"content":"【亮眼表现】\n我方打断对手获取先手次数为 15 次（对方 8 次），预判与反应双在线，对拼胜率领先。","jump_points":[1],"label_id":23},{"content":"【有待提升】\n本局炁满时累积伤害量：145（我方），579（对手），把握时机开大防止炁力浪费，炁满不释放会浪费输出，连段中及时开大提升总伤。","jump_points":[9],"is_rule":true,"label_id":29}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n被追平后迅速调整状态，连胜两局 3:1 锁定胜局。\n【优势点】博弈能力斩获 8.3 分，对手拿下 5.1 分，表现优于对手，且自身非常优秀。\n【劣势点】资源管理能力 6.3 分对对手 6.8 分，表现可圈可点，稍稍落后些许。", "is_rule": true}, {"content": "【亮眼表现】\n我方打断对手获取先手次数为 15 次（对方 8 次），预判与反应双在线，对拼胜率领先。", "jump_points": [1], "label_id": 23, "label_name": "打断对手获取先手次数"}, {"content": "【有待提升】\n在对手体力见底或连段压制时使用绝技，可以提升绝技命中率并扩大对局优势。", "jump_points": [2, 10], "is_rule": true, "label_id": 29, "label_name": "炁满时累积伤害量"}]}</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n0:1 落后扳回一局追平，后续崩盘 1:3 惜败。全局仍需提升，但是资源管理能力发挥出色。\n【优势点】资源管理能力 6.8 比 6.3 对阵对手，表现可圈可点，整体运营更具优势，资源分配更合理。\n【劣势点】博弈能力 5.1 分对比对手 8.3 分，调整思路后就能快速进步。","is_rule":true},{"content":"【亮眼表现】\n我方炁满时累积伤害 579（对手 145），关键时刻成功兑现爆发价值。","jump_points":[1],"label_id":29},{"content":"【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n0:1 落后扳回一局追平，最终1:3 遗憾告负。全局仍需提升，但是资源管理能力发挥出色。\n【优势点】资源管理能力 6.8 比 6.3 对阵对手，表现可圈可点，整体运营更具优势，资源分配更合理。\n【劣势点】博弈能力 5.1 分对比对手 8.3 分，坚持练习，对手绝非遥不可及。", "is_rule": true}, {"content": "【亮眼表现】\n我方炁满时累积伤害 579（对手 145），关键时刻将炁转化为伤害，利用率不俗。", "jump_points": [1], "label_id": 29, "label_name": "炁满时累积伤害量"}, {"content": "【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n势均力敌战至终章，关键发挥 3:2 险胜对手。\n【优势点】防守能力 6.3 分对对手 5.5 分，水准已然在线，防守表现略胜一筹。\n【劣势点】资源管理能力 6.4 分不敌对手 7.5 分，表现可圈可点，略有微小差距。","is_rule":true},{"content":"【亮眼表现】\n我方强制脱出后安全率为 76.9%（对手 58.3%），脱困后迅速稳住身位，生存意识拉满。","jump_points":[1],"label_id":19},{"content":"【有待提升】\n体力消耗较大，每次强制取消都会消耗2格体力，需要注意强制取消的使用时机。","jump_points":[4,9],"is_rule":true,"label_id":25}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n势均力敌战至终章，关键发挥 3:2 险胜对手。\n【优势点】防守能力 6.3 分对对手 5.5 分，水准已然在线，防守表现难分伯仲。\n【劣势点】资源管理能力 6.4 分不敌对手 7.5 分，表现可圈可点，略有微小差距。", "is_rule": true}, {"content": "【亮眼表现】\n我方强制脱出后安全率为 76.9%（对手 58.3%），脱困后迅速稳住身位，生存意识拉满。", "jump_points": [1], "label_id": 19, "label_name": "脱出后安全率"}, {"content": "【有待提升】\n体力消耗较大，每次强制取消都会消耗2格体力，需要注意强制取消的使用时机。", "jump_points": [4, 9], "is_rule": true, "label_id": 25, "label_name": "体力消耗"}]}</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程对抗十分激烈，最终惜败 2:3 憾负。\n【优势点】资源管理能力 7.5 分对对手 6.4 分，水准已然在线，略占优势。\n【劣势点】防守能力 5.5 分 vs 对手 6.3 分，整体抗压稍逊，防守细节可进一步优化。","is_rule":true},{"content":"【亮眼表现】\n我方炁满时累积伤害 592（对手 197），关键输出表现尚可。","jump_points":[1],"label_id":29},{"content":"【有待提升】\n防反触发次数较低，熟悉平招的防反时机，可在防御成功后及时打出防御反击进行反制。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程对抗十分激烈，最终 2:3 憾负。\n【优势点】资源管理能力 7.5 分对对手 6.4 分，水准已然在线，略占一丝优势。\n【劣势点】防守能力 5.5 分 vs 对手 6.3 分，整体抗压表现接近，防守细节可进一步优化。", "is_rule": true}, {"content": "【亮眼表现】\n我方炁满时累积伤害 592（对手 197），能更合理利用炁进行爆发。", "jump_points": [1], "label_id": 29, "label_name": "炁满时累积伤害量"}, {"content": "【有待提升】\n防反触发次数较低，熟悉平招的防反时机，可在防御成功后及时打出防御反击进行反制。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n落后局面奋力一搏，仍以 1:3 遗憾落败。你本场各项数据均低于对手，整体状态有待调整，继续努力提升实力。\n【劣势点】输出能力 4.3 分不敌对手 8.7 分，多加练习就能快速成长。","is_rule":true},{"content":"【亮眼表现】\n我方炁满时累积伤害 212（对手 48），关键输出表现尚可。","jump_points":[1],"label_id":29},{"content":"【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n落后局面奋力一搏，仍以 1:3 遗憾落败。你本场各项数据均低于对手，整体状态有待调整，继续努力提升实力。\n【劣势点】输出能力 4.3 分不敌对手 8.7 分，多加练习就能快速成长。", "is_rule": true}, {"content": "【亮眼表现】\n我方炁满时累积伤害 212（对手 48），能更合理利用炁进行爆发。", "jump_points": [1], "label_id": 29, "label_name": "炁满时累积伤害量"}, {"content": "【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n掌控全场节奏，抓住赛点机会，3:1 果断终结对决。本次对战你全方位压制对手数据，发挥亮眼，展现出更强劲的实力。\n【优势点】输出能力 8.7 分 vs 对手 4.3 分，输出表现一马当先，该维度发挥堪称顶尖。","is_rule":true},{"content":"【亮眼表现】\n我方本局连段成功率 79.2%（对手 41.2%），招式衔余更稳定，失误少。","jump_points":[1],"label_id":7},{"content":"【有待提升】\n炁满时累积伤害量 48，高于对手的 212，及时使用大招避免炁囤积，满炁不使用会降低爆发，连段可以接上大招。","jump_points":[9],"is_rule":true,"label_id":29}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n掌控全场节奏，抓住赛点机会，3:1 果断终结对决。本次对战你全方位压制对手数据，发挥亮眼，展现出更强劲的实力。\n【优势点】输出能力 8.7 分 vs 对手 4.3 分，输出表现一马当先，该维度发挥堪称顶尖。", "is_rule": true}, {"content": "【亮眼表现】\n我方本局连段成功率 79.2%（对手 41.2%），招式衔接更为稳定，失误少。", "jump_points": [1], "label_id": 7, "label_name": "连段成功率"}, {"content": "【有待提升】\n在对手体力见底或连段压制时使用绝技，可以提升绝技命中率并扩大对局优势。", "jump_points": [2, 10], "is_rule": true, "label_id": 29, "label_name": "炁满时累积伤害量"}]}</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n追平比分后状态下滑，最终 1:3 遗憾落败。整体稍显不足，但资源管理能力较为突出。\n【优势点】资源管理能力 7.5 分对对手 5.9 分，水准已然在线，略占优势。\n【劣势点】先手能力 4.7 分对阵对手 7.2 分，优化操作细节会更出彩。","is_rule":true},{"content":"【亮眼表现】\n我方炁满时累积伤害 516（对手 232），炁满利用效率较为稳定。","jump_points":[1],"label_id":29},{"content":"【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n开局失利后奋力追平，最终 1:3 遗憾落败。整体稍显不足，但资源管理能力表现突出。\n【优势点】资源管理能力 7.5 分对对手 5.9 分，水准已然在线，略占一丝优势。\n【劣势点】先手能力 4.7 分对阵对手 7.2 分，优化操作细节会更出彩。", "is_rule": true}, {"content": "【亮眼表现】\n我方炁满时累积伤害 516（对手 232），炁满利用效率较为稳定。", "jump_points": [1], "label_id": 29, "label_name": "炁满时累积伤害量"}, {"content": "【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n及时调整战术状态，连胜两局 3:1 锁定胜果。\n【优势点】先手能力拿下 7.2 分，对手收获 4.7 分，实战表现更出色，该维度发挥相当优秀。\n【劣势点】资源管理能力 5.9 分 vs 对手 7.5 分，运营节奏略显落后，资源转化效率仍可提升。","is_rule":true},{"content":"【亮眼表现】\n绝技命中率：我方 100%，敌方 0%，展现了对战斗节奏的极致掌控与冷静判断。","jump_points":[1],"label_id":5},{"content":"【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n及时调整战术状态，连胜两局 3:1 锁定胜果。\n【优势点】先手能力拿下 7.2 分，对手收获 4.7 分，实战表现更出色，精准的先手进攻助你压制对手。\n【劣势点】资源管理能力 5.9 分 vs 对手 7.5 分，运营节奏略显落后，资源转化效率仍可提升。", "is_rule": true}, {"content": "【亮眼表现】\n绝技命中率：我方 100%，敌方 0%，展现了对战斗节奏的极致掌控与冷静判断。", "jump_points": [1], "label_id": 5, "label_name": "绝技命中率"}, {"content": "【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n面对对手全面压制，全力抵抗仍 0:3 遗憾落败。全局仍需提升，但是资源管理能力发挥出色。\n【优势点】资源管理能力以 6.5 比 6.0 对阵对手，表现可圈可点，运营节奏把控更佳，资源调度更流畅。\n【劣势点】博弈能力 4.7 分对阵对手 8.0 分，稍加练习就能实现提升。","is_rule":true},{"content":"【亮眼表现】\n我方炁满时累积伤害 450（对手 182），关键输出表现尚可。","jump_points":[1],"label_id":29},{"content":"【有待提升】\n当前防反触发次数偏少，若能更好把握平招的防反时机，可在成功防御后打出反击压制对手。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n对手全面压制，0：3告负。全局仍需提升，但是资源管理能力发挥出色。\n【优势点】资源管理能力 6.5 比 6.0 对阵对手，表现可圈可点，运营节奏把控更佳，资源调度更流畅。\n【劣势点】博弈能力 4.7 分对阵对手 8.0 分，稍加练习就能实现提升。", "is_rule": true}, {"content": "【亮眼表现】\n我方炁满时累积伤害 450（对手 182），能更合理利用炁进行爆发。", "jump_points": [1], "label_id": 29, "label_name": "炁满时累积伤害量"}, {"content": "【有待提升】\n当前防反触发次数偏少，若能更好把握平招的防反时机，可在成功防御后打出反击压制对手。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程掌控节奏，不给对手任何机会，以 3:0 干净利落取胜。\n【优势点】博弈能力取得 8.0 分，对手拿下 4.7 分，表现更胜一筹，该维度展现超凡水准。\n【劣势点】资源管理能力 6.0 分 vs 对手 6.5 分，与对手表现略处下风。","is_rule":true},{"content":"【亮眼表现】\n我方打断对手获取先手次数为 17 次（对方 7 次），对拼判断更敏锐，强行扭转攻防态势。","jump_points":[1],"label_id":23},{"content":"【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程掌控节奏，不给对手任何机会，以 3:0 干净利落取胜。\n【优势点】博弈能力取得 8.0 分，对手拿下 4.7 分，表现高出一档，表现出了非凡的水准。\n【劣势点】资源管理能力 6.0 分 vs 对手 6.5 分，与对手差距不大。", "is_rule": true}, {"content": "【亮眼表现】\n我方打断对手获取先手次数为 17 次（对方 7 次），对拼时的判断更敏锐，可以强行扭转攻防态势。", "jump_points": [1], "label_id": 23, "label_name": "打断对手获取先手次数"}, {"content": "【有待提升】\n脱出后体力处于劣势，建议借助保护时间拉开距离调整节奏，贸然反击可能再次陷入被压制局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n绝境之中扳回一局，可惜未能逆转 1:3 告负。\n【优势点】防守能力 4.2 分对对手 3.2 分，防守表现稳健，防守意识稍占上风。\n【劣势点】博弈能力 6.4 分对比对手 7.4 分，表现可圈可点，稍稍落后些许。","is_rule":true},{"content":"【亮眼表现】\n我方强制脱出后安全率为 33.3%（对手 0%），应对压制的表现较为稳定。","jump_points":[1],"label_id":19},{"content":"【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n绝境之中扳回一局，可惜未能逆转 1:3 告负。\n【优势点】防守能力 4.2 分对对手 3.2 分，防守表现难分伯仲，防守意识十分接近。\n【劣势点】博弈能力 6.4 分对比对手 7.4 分，表现可圈可点，稍稍落后些许。", "is_rule": true}, {"content": "【亮眼表现】\n我方强制脱出后安全率为 33.3%（对手 0%），应对压制的表现较为稳定。", "jump_points": [1], "label_id": 19, "label_name": "脱出后安全率"}, {"content": "【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程胶着拉锯，最终凭借稳定发挥 3:2 险中求胜。\n【优势点】防守能力拿下 6.7 分，对手斩获 3.1 分，发挥更胜一筹，该维度竞技状态极佳。\n【劣势点】先手能力 6.0 分 vs 对手 7.1 分，整体表现略处下风。","is_rule":true},{"content":"【亮眼表现】\n我方强制脱出后安全率为 100%（对手 11.1%），脱困后迅速稳住身位，生存意识拉满。","jump_points":[1],"label_id":19},{"content":"【有待提升】\n本场绝技命中率：我方 50%，对手 100%，绝技释放仍需更加谨慎，绝技本身需要起手时间，连段中接绝技更稳、更不容易空。","jump_points":[2,9],"is_rule":true,"label_id":5}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程胶着拉锯，最终凭借稳定发挥 3:2 险中求胜。\n【优势点】防守能力拿下 6.7 分，对手斩获 3.1 分，发挥好于对手，有效防御了大部分攻势。\n【劣势点】先手能力 6.0 分 vs 对手 7.1 分，虽逊于对手但亦不远矣。", "is_rule": true}, {"content": "【亮眼表现】\n我方强制脱出后安全率为 100%（对手 11.1%），脱困后迅速稳住身位，生存意识拉满。", "jump_points": [1], "label_id": 19, "label_name": "脱出后安全率"}, {"content": "【有待提升】\n绝技命中率（我方 50%）低于对手（100%），绝技出手时机的把握还有提升空间。绝技出手前有准备时间，放在连段里用，更容易打中。", "jump_points": [2, 9], "is_rule": true, "label_id": 5, "label_name": "绝技命中率"}]}</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程胶着难分高下，可惜 2:3 惜败对手。\n【优势点】先手能力 7.1 比 6.0 与对手相持，发挥稳健扎实，稍占据上风。\n【劣势点】防守能力 3.1 分不敌对手 6.7 分，调整防守策略即可变强。","is_rule":true},{"content":"【亮眼表现】\n绝技命中率对比：我方 100% ，对手 50% 。命中率整体较为稳定。","jump_points":[1],"label_id":5},{"content":"【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程胶着难分高下，可惜 2:3 败于对手。\n【优势点】先手能力 7.1 比 6.0 与对手相持，发挥稳健扎实，稍稍占据上风。\n【劣势点】防守能力 3.1 分不敌对手 6.7 分，调整防守策略即可变强。", "is_rule": true}, {"content": "【亮眼表现】\n绝技命中率对比：我方 100% ，对手 50% ，绝技命中率整体较为稳定。", "jump_points": [1], "label_id": 5, "label_name": "绝技命中率"}, {"content": "【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程胶着拉锯，最终凭借稳定发挥 3:2 险中求胜。\n【优势点】防守能力拿下 6.9 分，对手收获 4.8 分，防守表现更稳固，该维度发挥十分突出。\n【劣势点】资源管理能力 5.4 分 vs 对手 6.0 分，运营节奏略显落后，资源转化效率仍可提升。","is_rule":true},{"content":"【亮眼表现】\n我方强制脱出后安全率为 83.3%（对手 50%），脱困后迅速稳住身位，不给对手续连机会。","jump_points":[1],"label_id":19},{"content":"【有待提升】\n当前防反触发次数偏少，若能更好把握平招的防反时机，可在成功防御后打出反击压制对手。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程胶着拉锯，最终凭借稳定发挥 3:2 险中求胜。\n【优势点】防守能力拿下 6.9 分，对手收获 4.8 分，防守表现更稳固，该维度发挥十分突出。\n【劣势点】资源管理能力 5.4 分 vs 对手 6.0 分，运营节奏略显落后，资源转化效率仍可提升。", "is_rule": true}, {"content": "【亮眼表现】\n我方强制脱出后安全率为 83.3%（对手 50%），脱困后处理意识较好，不给对手续连机会。", "jump_points": [1], "label_id": 19, "label_name": "脱出后安全率"}, {"content": "【有待提升】\n当前防反触发次数偏少，若能更好把握平招的防反时机，可在成功防御后打出反击压制对手。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程胶着难分高下，可惜 2:3 惜败对手。\n【优势点】资源管理能力以 6.0 比 5.4 对阵对手，表现可圈可点，运营节奏把控更佳，资源调度更流畅。\n【劣势点】防守能力 4.8 分不敌对手 6.9 分，调整防守策略即可变强。","is_rule":true},{"content":"【亮眼表现】\n我方炁满时累积伤害 1045（对手 149），对输出窗口的把控较为合理。","jump_points":[1],"label_id":29},{"content":"【有待提升】\n当前防反触发次数偏少，若能更好把握平招的防反时机，可在成功防御后打出反击压制对手。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程胶着难分高下，可惜 2:3 败于对手。\n【优势点】资源管理能力 6.0 比 5.4 对阵对手，表现可圈可点，运营节奏把控更佳，资源调度更流畅。\n【劣势点】防守能力 4.8 分不敌对手 6.9 分，调整防守策略即可变强。", "is_rule": true}, {"content": "【亮眼表现】\n我方炁满时累积伤害 1045（对手 149），对输出窗口的把控较为合理。", "jump_points": [1], "label_id": 29, "label_name": "炁满时累积伤害量"}, {"content": "【有待提升】\n当前防反触发次数偏少，若能更好把握平招的防反时机，可在成功防御后打出反击压制对手。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程未能找到破局机会，实力稍逊 0:3 告负。本场对局你的各项数据均未达到平均水准，整体发挥存在不足，后续多打磨操作细节，能有效提升竞技水平。","is_rule":true},{"content":"【亮眼表现】\n目前数据低于预期，各项数据均有上扬空间，稍加调整即可持续提升。","jump_points":[1]},{"content":"【有待提升】\n脱出后体力并不占优，可利用脱出后的保护拉开距离寻找机会，避免贸然反击再次被对手先手。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n未能找到破局机会，0：3告负。本场对局你的各项数据均未达到平均水准，整体发挥存在不足，后续多打磨操作细节，能有效提升竞技水平。", "is_rule": true}, {"content": "【亮眼表现】\n目前数据低于预期，各项数据均有上扬空间，稍加调整即可稳定提升。", "jump_points": [1]}, {"content": "【有待提升】\n脱出后体力并不占优，可利用脱出后的保护拉开距离寻找机会，避免贸然反击再次被对手先手。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程胶着难分高下，可惜 2:3 惜败对手。\n【优势点】输出能力 7.3 分对对手 6.5 分，水准已然在线，略占一丝优势。\n【劣势点】资源管理能力 7.2 分不敌对手 7.7 分，表现可圈可点，略有微小差距。","is_rule":true},{"content":"【亮眼表现】\n我方本局连段成功率 66.7%（对手 57.6%），连招衔接较为稳定，基本功表现尚可。","jump_points":[1],"label_id":7},{"content":"【有待提升】\n防反触发次数较低，熟悉平招的防反时机，可在防御成功后及时打出防御反击进行反制。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程胶着难分高下，可惜 2:3 败于对手。\n【优势点】输出能力 7.3 分对对手 6.5 分，水准已然在线，略占一丝优势。\n【劣势点】资源管理能力 7.2 分不敌对手 7.7 分，表现可圈可点，略有微小差距。", "is_rule": true}, {"content": "【亮眼表现】\n我方本局连段成功率 66.7%（对手 57.6%），连招衔接较为稳定，表现尚可。", "jump_points": [1], "label_id": 7, "label_name": "连段成功率"}, {"content": "【有待提升】\n防反触发次数较低，熟悉平招的防反时机，可在防御成功后及时打出防御反击进行反制。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程胶着拉锯，最终凭借稳定发挥 3:2 险中求胜。整体尚有差距，但资源管理能力表现较佳。\n【优势点】资源管理能力 7.7 分对对手 7.2 分，水准已然在线，略占优势。\n【劣势点】输出能力 6.5 分对比对手 7.3 分，输出表现略处下风，表现可圈可点。","is_rule":true},{"content":"【亮眼表现】\n我方处于无法脱出的受击状态共 31.2 秒（对手 44.5 秒），脱身与反打时机精准，压缩受制时长。","jump_points":[1],"label_id":28},{"content":"【有待提升】\n本局连段成功率：57.6%（我方），66.7%（对手），保证稳定输出，不妨把握倒地判定与取消时机，可以更稳定地把攻击转化为连段。","jump_points":[7,9],"is_rule":true,"label_id":7}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程胶着拉锯，最终凭借稳定发挥 3:2 险中求胜。整体尚有差距，但资源管理能力实力强劲。\n【优势点】资源管理能力 7.7 分对对手 7.2 分，水准已然在线，略占一丝优势。\n【劣势点】输出能力 6.5 分对比对手 7.3 分，输出表现不相上下，表现可圈可点。", "is_rule": true}, {"content": "【亮眼表现】\n我方处于无法脱出的受击状态共 31.2 秒（对手 44.5 秒），脱身与反打时机精准，压缩受制时长。", "jump_points": [1], "label_id": 28, "label_name": "无法脱出总受击时间"}, {"content": "【有待提升】\n在对手体力见底或连段中使用绝技，可以提升绝技命中率并扩大对局优势。", "jump_points": [2, 10], "is_rule": true, "label_id": 29, "label_name": "炁满时累积伤害量"}]}</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n奋力反击追至平局，决胜局遗憾 2:3 告负。\n【优势点】输出能力以 6.7 比 6.1 小幅领先，发挥稳健扎实，表现略胜一筹。\n【劣势点】防守能力 4.7 分 vs 对手 6.0 分，双方表现略有微小差距。","is_rule":true},{"content":"【亮眼表现】\n我方本局连段成功率 62.5%（对手 43.2%），稳定的连招衔接是你扎实功底的体现。","jump_points":[1],"label_id":7},{"content":"【有待提升】\n防反触发次数较低，熟悉平招的防反时机，可在防御成功后及时打出防御反击进行反制。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n奋力反击追至平局，决胜局遗憾 2:3 告负。\n【优势点】输出能力 6.7 比 6.1 小幅领先，发挥稳健扎实，双方旗鼓相当。\n【劣势点】防守能力 4.7 分 vs 对手 6.0 分，双方表现基本持平。", "is_rule": true}, {"content": "【亮眼表现】\n我方本局连段成功率 62.5%（对手 43.2%），稳定的连招衔接是基本功扎实的体现。", "jump_points": [1], "label_id": 7, "label_name": "连段成功率"}, {"content": "【有待提升】\n防反触发次数较低，熟悉平招的防反时机，可在防御成功后及时打出防御反击进行反制。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程给予对手极大压迫，鏖战五局 2:3 遗憾惜败。\n【优势点】资源管理能力 7.4 比 6.4 对阵对手，表现可圈可点，整体运营更具优势，资源分配更合理。\n【劣势点】输出能力 6.4 分对比对手 7.0 分，输出表现略处下风，表现可圈可点。","is_rule":true},{"content":"【亮眼表现】\n我方处于无法脱出的受击状态共 30.9 秒（对手 36.8 秒），有效减少了被连续压制的时间。","jump_points":[1],"label_id":28},{"content":"【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程给予对手极大压迫，鏖战五局 2:3 遗憾惜败。\n【优势点】资源管理能力 7.4 比 6.4 对阵对手，表现可圈可点，整体运营更具优势，资源分配更合理。\n【劣势点】输出能力 6.4 分对比对手 7.0 分，输出表现不相上下，表现可圈可点。", "is_rule": true}, {"content": "【亮眼表现】\n我方处于无法脱出的受击状态共 30.9 秒（对手 36.8 秒），有效减少了被连续压制的时间。", "jump_points": [1], "label_id": 28, "label_name": "无法脱出总受击时间"}, {"content": "【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n比分交替上升鏖战五局，最终 3:2 险胜对手。\n【优势点】输出能力 7.0 比 6.4 对阵对手，发挥稳健扎实，输出表现略胜一筹。\n【劣势点】资源管理能力 6.4 分不敌对手 7.4 分，表现可圈可点，略有微小差距。","is_rule":true},{"content":"【亮眼表现】\n我方本局连段成功率 73.5%（对手 54.5%），体现了更扎实的基本功与更冷静的临场判断。","jump_points":[1],"label_id":7},{"content":"【有待提升】\n本局无法脱出总受击时间：36.8s（我方），30.9s（对手），被连续压制时的应对能力有待加强，受击时观察对手节奏，减少无法脱出时间。","jump_points":[5,9],"is_rule":true,"label_id":28}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n比分交替上升鏖战五局，最终 3:2 险胜对手。\n【优势点】输出能力 7.0 比 6.4 与对手持平，发挥稳健扎实，输出表现势均力敌。\n【劣势点】资源管理能力 6.4 分不敌对手 7.4 分，表现可圈可点，略有微小差距。", "is_rule": true}, {"content": "【亮眼表现】\n我方本局连段成功率 73.5%（对手 54.5%），体现了更扎实的基本功与更冷静的临场判断。", "jump_points": [1], "label_id": 7, "label_name": "连段成功率"}, {"content": "【有待提升】\n本局无法脱出总受击时间：36.8s（我方），30.9s（对手），受制状态偏长，脱困意识与操作效率有待提高。无法脱出受击时间过长，要格外注意在低体力或强制脱出冷却时避免受击。", "jump_points": [5, 9], "is_rule": true, "label_id": 28, "label_name": "无法脱出总受击时间"}]}</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n战局几经波折，顶住压力连追两局 3:2 逆转。\n【优势点】防守能力以 6.8 比 4.8 领先，发挥稳健扎实，表现略胜一筹。\n【劣势点】输出能力 6.9 分 vs 对手 7.7 分，表现可圈可点，稍稍落后些许。","is_rule":true},{"content":"【亮眼表现】\n我方强制脱出后安全率为 83.3%（对手 50%），在摆脱受击状态时具备更好的生存把控。","jump_points":[1],"label_id":19},{"content":"【有待提升】\n本局最大连段伤害：270（我方），422（对手），可优化连招伤害构成，建议在普攻连段里穿插技能，或把绝技带进连段，伤害会明显更高。","jump_points":[8,9],"is_rule":true,"label_id":11}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n战局几经波折，最终重掌节奏以 3:2 锁定胜局。\n【优势点】防守能力 6.8 比 4.8 领先，发挥稳健扎实,势均力敌。\n【劣势点】输出能力 6.9 分 vs 对手 7.7 分，表现可圈可点，稍稍落后些许。", "is_rule": true}, {"content": "【亮眼表现】\n我方强制脱出后安全率为 83.3%（对手 50%），在摆脱受击状态时具备更好的生存把控。", "jump_points": [1], "label_id": 19, "label_name": "脱出后安全率"}, {"content": "【有待提升】\n在对手体力见底或处于连段中时使用绝技，可以提升绝技命中率并扩大对局优势。", "jump_points": [2, 10], "is_rule": true, "label_id": 29, "label_name": "炁满时累积伤害量"}]}</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程保持高压态势，不给反扑空间 3:0 轻松收官。\n【优势点】输出能力斩获 7.7 分，对手仅得 5.5 分，攻坚更占上风，该维度输出端表现优异。\n【劣势点】资源管理能力 5.2 分 vs 对手 5.7 分，运营节奏略显落后，资源转化效率仍可提升。","is_rule":true},{"content":"【亮眼表现】\n我方本局连段成功率 80.8%（对手 71.4%），在进攻端始终保持稳定输出。","jump_points":[1],"label_id":7},{"content":"【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n全程保持高压态势，不给反扑空间 3:0 轻松收官。\n【优势点】输出能力斩获 7.7 分，对手仅得 5.5 分，攻坚更占上风，该维度输出端表现优异。\n【劣势点】资源管理能力 5.2 分 vs 对手 5.7 分，运营节奏略显落后，资源转化效率仍可提升。", "is_rule": true}, {"content": "【亮眼表现】\n我方本局连段成功率 80.8%（对手 71.4%），在进攻端始终可以保持稳定输出，进攻能力出色。", "jump_points": [1], "label_id": 7, "label_name": "连段成功率"}, {"content": "【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n实力差距较为明显，拼尽全力仍 0:3 不敌对手。\n【优势点】资源管理能力 5.7 比 5.2 领先对手，运营表现稳健，资源把控稍占上风。\n【劣势点】输出能力 5.5 分对比对手 7.7 分，优化输出思路会更强势。","is_rule":true},{"content":"【亮眼表现】\n我方炁满时累积伤害 850（对手 109），对输出窗口的把控较为合理。","jump_points":[1],"label_id":29},{"content":"【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。","jump_points":[5,9],"is_rule":true,"label_id":18}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n实力差距较为明显， 0:3 不敌对手。\n【优势点】资源管理能力 5.7 比 5.2 领先对手，运营表现难分高下，资源把控都很到位。\n【劣势点】输出能力 5.5 分对比对手 7.7 分，优化输出思路会更强势。", "is_rule": true}, {"content": "【亮眼表现】\n我方炁满时累积伤害 850（对手 109），对输出窗口的把控较为合理。", "jump_points": [1], "label_id": 29, "label_name": "炁满时累积伤害量"}, {"content": "【有待提升】\n脱出后体力不占优势，可以利用脱出后的保护拉开距离寻找机会，贸然反击被再次先手会陷入无法脱出的不利局面。", "jump_points": [5, 9], "is_rule": true, "label_id": 18, "label_name": "脱出后反打成功率"}]}</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n三盘发挥毫无破绽，以 3:0 横扫对手拿下胜利。本场对战你数据全维度领先敌方，发挥稳定，彰显更强竞技水平。\n【优势点】博弈能力斩获 8.6 分，对手仅得 5.7 分，发挥更占优势，该维度表现极为亮眼。","is_rule":true},{"content":"【亮眼表现】\n我方打断对手获取先手次数为 10 次（对方 6 次），对拼判断更敏锐，强行扭转攻防态势。","jump_points":[1],"label_id":23},{"content":"【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n三盘发挥毫无破绽，以 3:0 横扫对手拿下胜利。本场对战你数据全维度领先敌方，发挥稳定，彰显更强竞技水平。\n【优势点】博弈能力斩获 8.6 分，对手仅得 5.7 分，发挥更占优势，全方位压制了对手。", "is_rule": true}, {"content": "【亮眼表现】\n我方打断对手获取先手次数为 10 次（对方 6 次），对拼时的判断更敏锐，可以强行扭转攻防态势。", "jump_points": [1], "label_id": 23, "label_name": "打断对手获取先手次数"}, {"content": "【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>{"sections":[{"content":"【整体评价】\n全程处于被动局面，奋力抵抗仍 0:3 遗憾告负。本次对战整体数据不及敌方，要总结经验，不断提升自身竞技水平。\n【劣势点】博弈能力 5.7 分对比对手 8.6 分，调整思路后就能快速进步。","is_rule":true},{"content":"【亮眼表现】\n全局表现尚有巨大余力，各项数据都有极高提升空间。","jump_points":[1]},{"content":"【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。","jump_points":[12,10],"is_rule":true,"label_id":14}]}</t>
+          <t>{"sections": [{"content": "【整体评价】\n实力差距较为明显，0：3告负。本次对战整体数据不及敌方，要总结经验，不断提升自身竞技水平。\n【劣势点】博弈能力 5.7 分对比对手 8.6 分，坚持练习，对手绝非遥不可及。", "is_rule": true}, {"content": "【亮眼表现】\n全局表现尚有上升余力，持续练习则能更进一步。", "jump_points": [1]}, {"content": "【有待提升】\n防反触发次数较低，熟悉平招的防反时机能够在防御成功后打出防御反击反制对手。", "jump_points": [12, 10], "is_rule": true, "label_id": 14, "label_name": "防御反击触发次数"}]}</t>
         </is>
       </c>
     </row>
